--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -2344,7 +2344,7 @@
         <v>121768106</v>
       </c>
       <c r="B16" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -2344,7 +2344,7 @@
         <v>121768106</v>
       </c>
       <c r="B16" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2463,6 +2463,434 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128075036</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97344</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sandsjötjärnen, Sandsjötjärnen, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>330976</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6417485</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128074785</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sandsjötjärnen, Sandsjötjärnen, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>330920</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6417443</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128075156</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56864</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sandsjötjärnen, Sandsjötjärnen, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>330977</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6417546</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128075226</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sandsjötjärnen, Sandsjötjärnen, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>330944</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6417540</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -2468,7 +2468,7 @@
         <v>128075036</v>
       </c>
       <c r="B17" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -2468,7 +2468,7 @@
         <v>128075036</v>
       </c>
       <c r="B17" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -2468,7 +2468,7 @@
         <v>128075036</v>
       </c>
       <c r="B17" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -2468,7 +2468,7 @@
         <v>128075036</v>
       </c>
       <c r="B17" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>128074785</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>128075226</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -2468,7 +2468,7 @@
         <v>128075036</v>
       </c>
       <c r="B17" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>128074785</v>
       </c>
       <c r="B18" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>128075156</v>
       </c>
       <c r="B19" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>128075226</v>
       </c>
       <c r="B20" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -2468,7 +2468,7 @@
         <v>128075036</v>
       </c>
       <c r="B17" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>128074785</v>
       </c>
       <c r="B18" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>128075156</v>
       </c>
       <c r="B19" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>128075226</v>
       </c>
       <c r="B20" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 563-2024 artfynd.xlsx
+++ b/artfynd/A 563-2024 artfynd.xlsx
@@ -2468,7 +2468,7 @@
         <v>128075036</v>
       </c>
       <c r="B17" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
